--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
+          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
+          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
+          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
+          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
+          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
+          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
+          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,22 +881,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
+          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
+          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
+          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
+          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
+          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
+          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,22 +977,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino to stand for reelection in 2027</t>
+          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gianni Infantino will run for reelection as FIFA president despite uncertainty over his future in the position following his failed attempt to raise $20 billion with the sale of a stake in future World Cups to private investors.</t>
+          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0906/r1712226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49847747/fifa-president-gianni-infantino-stand-re-election-2027</t>
+          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maresca: Enzo Fernandez is 'a winner'</t>
+          <t>FIFA president Gianni Infantino to stand for reelection in 2027</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maresca: Enzo Fernandez is 'a winner'</t>
+          <t>Gianni Infantino will run for reelection as FIFA president despite uncertainty over his future in the position following his failed attempt to raise $20 billion with the sale of a stake in future World Cups to private investors.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0904/dm_260904_Maresca_Enzo_Fernandez_is_a_winner/dm_260904_Maresca_Enzo_Fernandez_is_a_winner.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0906/r1712226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49824937/enzo-fernandez-winner</t>
+          <t>https://www.espn.com/soccer/story/_/id/49847747/fifa-president-gianni-infantino-stand-re-election-2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FIFA accuses UEFA of 'smear campaign' in opposing discovery request</t>
+          <t>Maresca: Enzo Fernandez is 'a winner'</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FIFA accused European soccer body UEFA of a "smear campaign" in a court filing Thursday concerning FIFA president Gianni Infantino's failed plan to sell stakes in the World Cup and other competitions.</t>
+          <t>Maresca: Enzo Fernandez is 'a winner'</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0903/r1711044_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0904/dm_260904_Maresca_Enzo_Fernandez_is_a_winner/dm_260904_Maresca_Enzo_Fernandez_is_a_winner.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49817156/fifa-uefa-legal-filing-discovery-world-cup-sell-stake</t>
+          <t>https://www.espn.com/video/clip/_/id/49824937/enzo-fernandez-winner</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Socceroos transfer tracker: Where Australia's stars will play in 2026-27</t>
+          <t>FIFA accuses UEFA of 'smear campaign' in opposing discovery request</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Transfer deadlines are hitting across the globe and, with it, bringing to an end a window that has seen a remarkable surge in interest in players who represented the Socceroos at the FIFA World Cup.</t>
+          <t>FIFA accused European soccer body UEFA of a "smear campaign" in a court filing Thursday concerning FIFA president Gianni Infantino's failed plan to sell stakes in the World Cup and other competitions.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0902/r1710219_1295x729_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0903/r1711044_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49466177/socceroos-transfer-tracker-where-australias-stars-play-2026-27</t>
+          <t>https://www.espn.com/soccer/story/_/id/49817156/fifa-uefa-legal-filing-discovery-world-cup-sell-stake</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kushner says he regrets role in FIFA's World Cup sell-off plan</t>
+          <t>Socceroos transfer tracker: Where Australia's stars will play in 2026-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FIFA's intended investment partner, Josh Kushner, said he regrets getting involved in Gianni Infantino's failed World Cup sell-off plan.</t>
+          <t>Transfer deadlines are hitting across the globe and, with it, bringing to an end a window that has seen a remarkable surge in interest in players who represented the Socceroos at the FIFA World Cup.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0901/r1710146_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0902/r1710219_1295x729_16-9.png</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49796943/fifa-world-cup-sell-josh-kushner-gianni-infantino</t>
+          <t>https://www.espn.com/soccer/story/_/id/49466177/socceroos-transfer-tracker-where-australias-stars-play-2026-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,22 +1137,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gomez: Nobody should wear the Argentina No. 10 jersey for quite some time!</t>
+          <t>Kushner says he regrets role in FIFA's World Cup sell-off plan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gomez: Nobody should wear the Argentina No. 10 jersey for quite some time!</t>
+          <t>FIFA's intended investment partner, Josh Kushner, said he regrets getting involved in Gianni Infantino's failed World Cup sell-off plan.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0901/dm_260901_Gomez_Nobody_should_wear_the_Argentina_number_10_jersey_for_quite_some_time/dm_260901_Gomez_Nobody_should_wear_the_Argentina_number_10_jersey_for_quite_some_time.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0901/r1710146_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49793781/wear-argentina-no-10-jersey-quite-some</t>
+          <t>https://www.espn.com/soccer/story/_/id/49796943/fifa-world-cup-sell-josh-kushner-gianni-infantino</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lionel Messi's Argentina career: the stats, records and how he compares to Cristiano Ronaldo</t>
+          <t>Gomez: Nobody should wear the Argentina No. 10 jersey for quite some time!</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>After Lionel Messi announced his international retirement, ESPN takes a look at the numbers behind his storied Argentina career.</t>
+          <t>Gomez: Nobody should wear the Argentina No. 10 jersey for quite some time!</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0831/r1709497_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0901/dm_260901_Gomez_Nobody_should_wear_the_Argentina_number_10_jersey_for_quite_some_time/dm_260901_Gomez_Nobody_should_wear_the_Argentina_number_10_jersey_for_quite_some_time.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49784066/lionel-messi-argentina-career-stats-records-how-compares-cristiano-ronaldo</t>
+          <t>https://www.espn.com/video/clip/_/id/49793781/wear-argentina-no-10-jersey-quite-some</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly as 'last tango' farewell</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
+          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
+          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
+          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
+          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
+          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
+          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
+          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
+          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
+          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
+          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino to stand for reelection in 2027</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gianni Infantino will run for reelection as FIFA president despite uncertainty over his future in the position following his failed attempt to raise $20 billion with the sale of a stake in future World Cups to private investors.</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0906/r1712226_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49847747/fifa-president-gianni-infantino-stand-re-election-2027</t>
+          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maresca: Enzo Fernandez is 'a winner'</t>
+          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Maresca: Enzo Fernandez is 'a winner'</t>
+          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0904/dm_260904_Maresca_Enzo_Fernandez_is_a_winner/dm_260904_Maresca_Enzo_Fernandez_is_a_winner.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49824937/enzo-fernandez-winner</t>
+          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FIFA accuses UEFA of 'smear campaign' in opposing discovery request</t>
+          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FIFA accused European soccer body UEFA of a "smear campaign" in a court filing Thursday concerning FIFA president Gianni Infantino's failed plan to sell stakes in the World Cup and other competitions.</t>
+          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0903/r1711044_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49817156/fifa-uefa-legal-filing-discovery-world-cup-sell-stake</t>
+          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Socceroos transfer tracker: Where Australia's stars will play in 2026-27</t>
+          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Transfer deadlines are hitting across the globe and, with it, bringing to an end a window that has seen a remarkable surge in interest in players who represented the Socceroos at the FIFA World Cup.</t>
+          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0902/r1710219_1295x729_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49466177/socceroos-transfer-tracker-where-australias-stars-play-2026-27</t>
+          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kushner says he regrets role in FIFA's World Cup sell-off plan</t>
+          <t>FIFA president Gianni Infantino to stand for reelection in 2027</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FIFA's intended investment partner, Josh Kushner, said he regrets getting involved in Gianni Infantino's failed World Cup sell-off plan.</t>
+          <t>Gianni Infantino will run for reelection as FIFA president despite uncertainty over his future in the position following his failed attempt to raise $20 billion with the sale of a stake in future World Cups to private investors.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0901/r1710146_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0906/r1712226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49796943/fifa-world-cup-sell-josh-kushner-gianni-infantino</t>
+          <t>https://www.espn.com/soccer/story/_/id/49847747/fifa-president-gianni-infantino-stand-re-election-2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gomez: Nobody should wear the Argentina No. 10 jersey for quite some time!</t>
+          <t>Maresca: Enzo Fernandez is 'a winner'</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gomez: Nobody should wear the Argentina No. 10 jersey for quite some time!</t>
+          <t>Maresca: Enzo Fernandez is 'a winner'</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0901/dm_260901_Gomez_Nobody_should_wear_the_Argentina_number_10_jersey_for_quite_some_time/dm_260901_Gomez_Nobody_should_wear_the_Argentina_number_10_jersey_for_quite_some_time.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0904/dm_260904_Maresca_Enzo_Fernandez_is_a_winner/dm_260904_Maresca_Enzo_Fernandez_is_a_winner.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49793781/wear-argentina-no-10-jersey-quite-some</t>
+          <t>https://www.espn.com/video/clip/_/id/49824937/enzo-fernandez-winner</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,22 +721,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly as 'last tango' farewell</t>
+          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -753,22 +753,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly as 'last tango' farewell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -785,22 +785,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,22 +881,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
+          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
+          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
+          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
+          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
+          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
+          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,22 +977,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
+          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
+          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
+          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
+          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
+          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
+          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
+          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
+          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
+          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
+          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,22 +1137,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino to stand for reelection in 2027</t>
+          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gianni Infantino will run for reelection as FIFA president despite uncertainty over his future in the position following his failed attempt to raise $20 billion with the sale of a stake in future World Cups to private investors.</t>
+          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0906/r1712226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49847747/fifa-president-gianni-infantino-stand-re-election-2027</t>
+          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maresca: Enzo Fernandez is 'a winner'</t>
+          <t>FIFA president Gianni Infantino to stand for reelection in 2027</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maresca: Enzo Fernandez is 'a winner'</t>
+          <t>Gianni Infantino will run for reelection as FIFA president despite uncertainty over his future in the position following his failed attempt to raise $20 billion with the sale of a stake in future World Cups to private investors.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0904/dm_260904_Maresca_Enzo_Fernandez_is_a_winner/dm_260904_Maresca_Enzo_Fernandez_is_a_winner.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0906/r1712226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49824937/enzo-fernandez-winner</t>
+          <t>https://www.espn.com/soccer/story/_/id/49847747/fifa-president-gianni-infantino-stand-re-election-2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -753,7 +753,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly as 'last tango' farewell</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
+          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
+          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
+          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
+          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,22 +913,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
+          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
+          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
+          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
+          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
+          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
+          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,22 +1009,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
+          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
+          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
+          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
+          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,22 +1073,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
+          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
+          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
+          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
+          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
+          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
+          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
+          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,22 +1169,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino to stand for reelection in 2027</t>
+          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gianni Infantino will run for reelection as FIFA president despite uncertainty over his future in the position following his failed attempt to raise $20 billion with the sale of a stake in future World Cups to private investors.</t>
+          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0906/r1712226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49847747/fifa-president-gianni-infantino-stand-re-election-2027</t>
+          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
+          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
+          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
+          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
+          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,22 +881,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,22 +721,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
+          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
+          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
+          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
+          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
+          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,22 +913,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
+          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Burley: Kane should win the 2026 men's Ballon d'Or</t>
+          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0909/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL/dm_260909_COM_SOC_Analysis_Burley_Kane_should_win_the_2026_mens_Ballon_dOr_20260909_GLOBAL.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49877552/kane-win-2026-men-ballon-dor</t>
+          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Popovic comfortable with Socceroos penalty shootout choices at World Cup</t>
+          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Socceroos coach Tony Popovic isn't second-guessing the shootout that saw his side eliminated from the FIFA World Cup, saying that he would have made the same choices had the two sides come back the next day.</t>
+          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713099_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49865329/popovic-comfortable-socceroos-penalty-shootout-choices-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cape Verde's Vozinha nominated for Goalkeeper of the Year award at Ballon d'Or after World Cup heroics</t>
+          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cape Verde goalkeeper Vozinha has been nominated for the men's Goalkeeper of the Year award at the 2026 Ballon d'Or.</t>
+          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713164_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49868020/cape-verde-colo-colo-vozinha-nominated-goalkeeper-year-award</t>
+          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Belgian FA won't back Infantino's FIFA reelection, cites Balogun red card ban U-turn</t>
+          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Belgian football federation said it can't support Gianni Infantino's bid for another term as FIFA president, citing transparency and governance issues and the way FIFA handled clearing Folarin Balogun from a mandatory one-game ban at the World Cup.</t>
+          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0907/r1712695_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49857842/gianni-infantino-fifa-belgian-fa-belgium-world-cup-2026-folarin-balogun-red-card-overturned-usmnt</t>
+          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Socceroos stalwart Ryan axed for Brazil series</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
+          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,22 +753,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
+          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -785,22 +785,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
+          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
+          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
+          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
+          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
+          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
+          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
+          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
+          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
+          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,22 +1009,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
+          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
+          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
+          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
+          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
+          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
+          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,22 +1169,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026 Ballon d'Or: Full men's, women's short lists, host city change, more</t>
+          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The 2026 Ballon d'Or short lists are out. Here's who could win the biggest individual prizes in men's and women's soccer.</t>
+          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0908/r1713144_2_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49867974/2026-ballon-dor-full-mens-women-shortlists-host-city-change-vozinha-more</t>
+          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,22 +721,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Socceroos stalwart Ryan axed for Brazil series</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
+          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
+          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
+          <t>Socceroos stalwart Ryan axed for Brazil series</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
+          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
+          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
+          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,22 +881,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
+          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
+          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
+          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
+          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ecuador hires Marcelo Gallardo through 2030 World Cup</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marcelo Gallardo, one of the most decorated coaches in the history of the Argentine league, has reached an agreement to manage Ecuador ahead of the 2030 FIFA World Cup.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0914/r1716613_1024x576_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49941399/ecuador-hires-marcelo-gallardo-2030-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Two FIFA officials get lifetime bans for misuse of funds</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FIFA judges imposed life bans on two former federation presidents for financial misconduct.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0701/r1682659_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49905396/two-fifa-officials-get-life-bans-misuse-funds</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FIFA: 2030 World Cup final host country decision to be made 'in due course'</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FIFA said on Thursday that the decision over whether Morocco or Spain would host the 2030 World Cup final would be made "in due course."</t>
+          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0313/r1627854_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49892754/fifa-decision-morocco-vs-spain-host-2030-world-cup-final-made-due-course</t>
+          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,22 +753,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -785,22 +785,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
+          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Socceroos stalwart Ryan axed for Brazil series</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
+          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Socceroos stalwart Ryan axed for Brazil series</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
+          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,22 +881,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
+          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -913,22 +913,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
+          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
+          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
+          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -945,22 +945,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
+          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
+          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -977,22 +977,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Infantino open to FIFA governance review, reforms after backlash</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,22 +785,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
+          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Socceroos stalwart Ryan axed for Brazil series</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
+          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Socceroos stalwart Ryan axed for Brazil series</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
+          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,22 +913,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
+          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -945,22 +945,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
+          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
+          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
+          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -977,22 +977,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
+          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
+          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
+          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
+          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
+          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
+          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
+          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
+          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,22 +1137,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>James Rodríguez retires from Colombia after 15-year career</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1169,22 +1169,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is not the No. 9 Barcelona wanted, but the one they needed</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0915/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed/dm_260915_Gomez_Raphinha_is_not_the_No_9_Barcelona_wanted_but_the_one_they_needed.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49947635/raphinha-not-no-9-barcelona-wanted-one-needed</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,22 +721,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Infantino open to FIFA governance review, reforms after backlash</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
+          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Gomez: Raphinha is the best player in the world</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Gomez: Raphinha is the best player in the world</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/video/clip/_/id/50004079/raphinha-best-player-world</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>Infantino open to FIFA governance review, reforms after backlash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
+          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Socceroos stalwart Ryan axed for Brazil series</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
+          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
+          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
+          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
+          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
+          <t>Socceroos stalwart Ryan axed for Brazil series</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
+          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
+          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Thomas Tuchel: 'Regret I didn't eat some grass' after England's Azteca win over Mexico</t>
+          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thomas Tuchel has revealed he wished he had eaten some of the grass after England's memorable FIFA World Cup win over Mexico.</t>
+          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717253_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952392/thomas-tuchel-wish-ate-some-azteca-grass-england-stunning-world-cup-win-mexico</t>
+          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lionel Messi called up for Oct. 6 Argentina friendly for 'last tango'</t>
+          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Despite announcing his international retirement, Lionel Messi was included Tuesday in Argentina's squad for a farewell friendly against Benin on Oct. 6.</t>
+          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1717226_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49952015/lionel-messi-called-argentina-friendly-last-tango-farewell</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>James Rodríguez retires from Colombia after 15-year career</t>
+          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>James Rodríguez announced his retirement from Colombia's national team on Tuesday after 15 years on the international stage.</t>
+          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0205/r1610909_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49950986/james-rodriguez-retires-colombia</t>
+          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
+          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is the best player in the world</t>
+          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is the best player in the world</t>
+          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004079/raphinha-best-player-world</t>
+          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
+          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Infantino open to FIFA governance review, reforms after backlash</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
+          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Gomez: Raphinha is the best player in the world</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Gomez: Raphinha is the best player in the world</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/video/clip/_/id/50004079/raphinha-best-player-world</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>Infantino open to FIFA governance review, reforms after backlash</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
+          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Socceroos stalwart Ryan axed for Brazil series</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sources: English FA chief demands documents on FIFA World Cup sell-off plan, Balogun decision</t>
+          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FIFA vice president and FA chairwoman Debbie Hewitt has demanded FIFA president Gianni Infantino release all documents concerning his proposal for private investors to buy stakes in the World Cup, sources told ESPN.</t>
+          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1718041_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49964525/fa-chief-demands-gianni-infantino-releases-fifa-documents-private-equity-proposal-folarin-balogun-decision</t>
+          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA VP: Gianni Infantino World Cup plan 'struck at the heart of the game'</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gianni Infantino's plan to sell off a stake in the World Cup "struck at the very heart of the principles of the game," UEFA vice-president Laura McAllister has told ESPN.</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963369/uefa-vp-laura-mcallister-gianni-infantino-world-cup-plan-struck-very-heart-game</t>
+          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta says Camp Nou should host 2030 World Cup final</t>
+          <t>Socceroos stalwart Ryan axed for Brazil series</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Barcelona president Joan Laporta has argued that the Camp Nou should host the 2030 World Cup final.</t>
+          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0917/r1717980_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49963173/barcelona-president-joan-laporta-camp-nou-host-2030-world-cup-final</t>
+          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel defends subs vs. Argentina: 'It's my scar'</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>England boss Thomas Tuchel said he stands by his heavily criticised defensive substitutions in the World Cup semifinal defeat to Argentina, but accepts he made them too early.</t>
+          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0916/r1717694_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49959154/england-thomas-tuchel-argentina-substitutions-2026-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
+          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
+          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,22 +753,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
+          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
+          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
+          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -785,22 +785,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
+          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
+          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
+          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,22 +881,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is the best player in the world</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is the best player in the world</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004079/raphinha-best-player-world</t>
+          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -913,22 +913,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Gomez: Raphinha is the best player in the world</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Gomez: Raphinha is the best player in the world</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
+          <t>https://www.espn.com/video/clip/_/id/50004079/raphinha-best-player-world</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -945,22 +945,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -977,22 +977,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Infantino open to FIFA governance review, reforms after backlash</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Infantino open to FIFA governance review, reforms after backlash</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,22 +1073,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1105,22 +1105,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
+          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1137,22 +1137,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Socceroos stalwart Ryan axed for Brazil series</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
+          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
+          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Socceroos stalwart Ryan axed for Brazil series</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inter Miami manager: 'It would be only fair' for Messi to win Ballon d'Or again</t>
+          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again/dm_260917_Inter_Miami_manager_It_would_be_only_fair_for_Messi_to_win_Ballon_dOr_again.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49964659/only-fair-messi-win-ballon-dor-again</t>
+          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
+          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
+          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
+          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
+          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
+          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
+          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
+          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
+          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
+          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
+          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
+          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
+          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
+          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is the best player in the world</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gomez: Raphinha is the best player in the world</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world/dm_260922_Gomez_Raphinha_is_the_best_player_in_the_world.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004079/raphinha-best-player-world</t>
+          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
+          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,22 +977,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1009,22 +1009,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Infantino open to FIFA governance review, reforms after backlash</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
+          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>Infantino open to FIFA governance review, reforms after backlash</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,22 +1137,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tuchel: No point in torturing ourselves over World Cup exit</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit/dm_260918_Tuchel_No_point_in_torturing_ourselves_over_World_Cup_exit.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49972364/no-point-torturing-ourselves-world-cup-exit</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1169,22 +1169,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Socceroos stalwart Ryan axed for Brazil series</t>
+          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maty Ryan has been axed from the Socceroos squad to take on Brazil in Queensland. ESPN's Joey Lynch reacts to the squad announcement.</t>
+          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0917/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918/dm_260917_Soccer_Analysis_Socceroos_stalwart_Ryan_axed_for_Brazil_series_20260918.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49969083/socceroos-stalwart-ryan-axed-brazil-series</t>
+          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0926/ss_20260926_205309109_36763731284/ss_20260926_205309109_36763731284.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/50038230/usmnt-debutants-made-their-mark-4-1-win-vs-peru</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,22 +753,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
+          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
+          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
+          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -785,22 +785,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
+          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
+          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
+          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
+          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
+          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
+          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
+          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,22 +881,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
+          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
+          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
+          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -913,22 +913,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
+          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -945,22 +945,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
+          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
+          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,22 +1009,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
+          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1073,22 +1073,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Infantino open to FIFA governance review, reforms after backlash</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Infantino open to FIFA governance review, reforms after backlash</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,22 +1169,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA, Concacaf call on Infantino to make $10m payments to all FIFA members</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FIFA's member federations should each get an extra $10 million (£7.4m) from its swelling cash reserves after a successful World Cup, the soccer body's vice presidents from Europe and North America said in a letter Friday.</t>
+          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0918/r1718671_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49974050/uefa-concacaf-call-infantino-make-10m-payments-all-fifa-members</t>
+          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,22 +721,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
+          <t>If FIFA expands the World Cup again, how would a 64-team tournament work?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
+          <t>The 2026 World Cup was the first to feature 48 teams, and 2030 could see the field swell to 64, but just how feasible is a tournament that size?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0926/ss_20260926_205309109_36763731284/ss_20260926_205309109_36763731284.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720423_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50038230/usmnt-debutants-made-their-mark-4-1-win-vs-peru</t>
+          <t>https://www.espn.com/soccer/story/_/id/50005268/if-fifa-expands-world-cup-again-how-64-team-tournament-work</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0926/ss_20260926_205309109_36763731284/ss_20260926_205309109_36763731284.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/50038230/usmnt-debutants-made-their-mark-4-1-win-vs-peru</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,22 +785,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
+          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
+          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
+          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
+          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
+          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
+          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
+          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
+          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
+          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
+          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,22 +913,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
+          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
+          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
+          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -945,22 +945,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
+          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -977,22 +977,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
+          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
+          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,22 +1041,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
+          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1073,22 +1073,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1105,22 +1105,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Infantino open to FIFA governance review, reforms after backlash</t>
+          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
+          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
+          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Infantino open to FIFA governance review, reforms after backlash</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Patrick Vieira insists he expects to win trophies as Senegal boss</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0918/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA/dm_260918_COM_SOC_Presser_Patrick_Vieira_insists_he_expects_to_win_trophies_as_Senegal_boss_20260918_GLOBA.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/49974557/patrick-vieira-insists-expects-win-trophies-senegal-boss</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>If FIFA expands the World Cup again, how would a 64-team tournament work?</t>
+          <t>FIFA agrees in principle to federation payments from WC windfall</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The 2026 World Cup was the first to feature 48 teams, and 2030 could see the field swell to 64, but just how feasible is a tournament that size?</t>
+          <t>FIFA president Gianni Infantino has come out in favor of a tentative proposal from UEFA and Concacaf that FIFA distributes funds to member associations as a result of record revenues from this summer's World Cup.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720423_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0827/r1707823_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50005268/if-fifa-expands-world-cup-again-how-64-team-tournament-work</t>
+          <t>https://www.espn.com/soccer/story/_/id/50054758/fifa-agrees-federation-payments-wc-revenue</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
+          <t>Will anyone stop Infantino? FIFA president is confident U20 World Cup cameo says otherwise</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
+          <t>Under fire from UEFA, Infantino is back to business as usual and inching closer to reelection as FIFA president.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0926/ss_20260926_205309109_36763731284/ss_20260926_205309109_36763731284.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0927/r1722644_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50038230/usmnt-debutants-made-their-mark-4-1-win-vs-peru</t>
+          <t>https://www.espn.com/soccer/story/_/id/50045992/gianni-infantino-fifa-president-scandal-u20-world-cup-uefa-victor-montigliani</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
+          <t>Vozinha struggling with World Cup fame: 'I'd choose the life I had before'</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
+          <t>Viral World Cup goalkeeper Vozinha has revealed he is struggling with his newfound fame, saying that he would like to go back to a time before he was so well-known.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0928/r1722870_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/50050816/vozinha-world-cup-fame-struggling-cape-verde</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,27 +817,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0928/r1722794_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
+          <t>If FIFA expands the World Cup again, how would a 64-team tournament work?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
+          <t>The 2026 World Cup was the first to feature 48 teams, and 2030 could see the field swell to 64, but just how feasible is a tournament that size?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720423_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
+          <t>https://www.espn.com/soccer/story/_/id/50005268/if-fifa-expands-world-cup-again-how-64-team-tournament-work</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0926/ss_20260926_205309109_36763731284/ss_20260926_205309109_36763731284.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
+          <t>https://www.espn.com/video/clip/_/id/50038230/usmnt-debutants-made-their-mark-4-1-win-vs-peru</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
+          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
+          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
+          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
+          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
+          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
+          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
+          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
+          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
+          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
+          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>De la Fuente: The best is yet to come for the Spanish national team</t>
+          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0/dm_260922_COM_SOC_Analysis_De_la_Fuente3A_The_best_is_yet_to_come_for_the_Spanish_national_team_GLOBAL_2026-0.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50003632/best-yet-come-spanish-national-team</t>
+          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Grading Bafana Bafana players' overseas moves since the FIFA World Cup</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>South Africa returned to the FIFA World Cup in 2026 after a 16-year absence, and since their round of 32 exit at the hands of Canada, Bafana Bafana players have secured several noteworthy moves abroad.</t>
+          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0915/r1716934_1158x651_16-9.png</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49947673/grading-bafana-bafana-players-overseas-moves-fifa-world-cup</t>
+          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,27 +1137,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Infantino open to FIFA governance review, reforms after backlash</t>
+          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FIFA President Gianni Infantino has indicated he'd be open to an independent review of its governance system and signaled a willingness to consider reforms.</t>
+          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0806/r1698399_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50001668/infantino-open-fifa-governance-review-reforms-backlash</t>
+          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0617/r1674593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/fifa/fifa_data.xlsx
+++ b/fifa/fifa_data.xlsx
@@ -721,27 +721,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FIFA agrees in principle to federation payments from WC windfall</t>
+          <t>PSG chief Al-Khelaifi has 'zero interest' in FIFA presidency</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino has come out in favor of a tentative proposal from UEFA and Concacaf that FIFA distributes funds to member associations as a result of record revenues from this summer's World Cup.</t>
+          <t>European soccer's search for a candidate to challenge Gianni Infantino in the FIFA presidential election will not land on clubs' leader Nasser Al-Khelaifi.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0827/r1707823_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0929/r1723629_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50054758/fifa-agrees-federation-payments-wc-revenue</t>
+          <t>https://www.espn.com/soccer/story/_/id/50061434/fifa-president-nasser-al-khelaifi-psg-gianni-infantino-election</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -753,27 +753,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Will anyone stop Infantino? FIFA president is confident U20 World Cup cameo says otherwise</t>
+          <t>Pochettino labels Man City's charges as a 'period of deception'</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Under fire from UEFA, Infantino is back to business as usual and inching closer to reelection as FIFA president.</t>
+          <t>Pochettino labels Man City's charges as a 'period of deception'</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0927/r1722644_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0929/dm_260929_COM_SOC_Presser_Pochettino_labels_Man_Citys_charges_as_a_period_of_deception_20260929_GLOBAL/dm_260929_COM_SOC_Presser_Pochettino_labels_Man_Citys_charges_as_a_period_of_deception_20260929_GLOBAL.jpg</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50045992/gianni-infantino-fifa-president-scandal-u20-world-cup-uefa-victor-montigliani</t>
+          <t>https://www.espn.com/video/clip/_/id/50058472/pochettino-labels-man-city-charges-period-deception</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,27 +785,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vozinha struggling with World Cup fame: 'I'd choose the life I had before'</t>
+          <t>U.S. Soccer's post-World Cup vibes: Lamenting a missed opportunity, embracing excitement</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viral World Cup goalkeeper Vozinha has revealed he is struggling with his newfound fame, saying that he would like to go back to a time before he was so well-known.</t>
+          <t>The USMNT's World Cup was a paradox. Did inspiring a nation of future fans make it a success, or does the embarrassing exit mean it was a failure?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0928/r1722870_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0924/r1721313_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50050816/vozinha-world-cup-fame-struggling-cape-verde</t>
+          <t>https://www.espn.com/soccer/story/_/id/50020939/us-soccer-men-national-team-post-world-cup-vibes-lamenting-missed-opportunity-embracing-excitement</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -817,22 +817,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Messi tracker: Goals, assists, key moments in 2026</t>
+          <t>FIFA agrees in principle to federation payments from WC windfall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
+          <t>FIFA president Gianni Infantino has come out in favor of a tentative proposal from UEFA and Concacaf that FIFA distributes funds to member associations as a result of record revenues from this summer's World Cup.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0928/r1722794_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0827/r1707823_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
+          <t>https://www.espn.com/soccer/story/_/id/50054758/fifa-agrees-federation-payments-wc-revenue</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -849,27 +849,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>If FIFA expands the World Cup again, how would a 64-team tournament work?</t>
+          <t>Will anyone stop Infantino? FIFA president is confident U20 World Cup cameo says otherwise</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The 2026 World Cup was the first to feature 48 teams, and 2030 could see the field swell to 64, but just how feasible is a tournament that size?</t>
+          <t>Under fire from UEFA, Infantino is back to business as usual and inching closer to reelection as FIFA president.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720423_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0927/r1722644_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50005268/if-fifa-expands-world-cup-again-how-64-team-tournament-work</t>
+          <t>https://www.espn.com/soccer/story/_/id/50045992/gianni-infantino-fifa-president-scandal-u20-world-cup-uefa-victor-montigliani</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -881,27 +881,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
+          <t>Vozinha struggling with World Cup fame: 'I'd choose the life I had before'</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
+          <t>Viral World Cup goalkeeper Vozinha has revealed he is struggling with his newfound fame, saying that he would like to go back to a time before he was so well-known.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0926/ss_20260926_205309109_36763731284/ss_20260926_205309109_36763731284.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0928/r1722870_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50038230/usmnt-debutants-made-their-mark-4-1-win-vs-peru</t>
+          <t>https://www.espn.com/soccer/story/_/id/50050816/vozinha-world-cup-fame-struggling-cape-verde</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -913,27 +913,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
+          <t>Messi tracker: Goals, assists, key moments in 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
+          <t>ESPN provides game-by-game analysis of Lionel Messi's performances for Inter Miami and Argentina.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0928/r1722794_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
+          <t>https://www.espn.com/soccer/story/_/id/47978642/lionel-messi-2026-tracker-inter-miami-argentina-games-goals-assists-stats</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -945,27 +945,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
+          <t>If FIFA expands the World Cup again, how would a 64-team tournament work?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
+          <t>The 2026 World Cup was the first to feature 48 teams, and 2030 could see the field swell to 64, but just how feasible is a tournament that size?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720423_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
+          <t>https://www.espn.com/soccer/story/_/id/50005268/if-fifa-expands-world-cup-again-how-64-team-tournament-work</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -977,27 +977,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
+          <t>Herc Gomez: USMNT debutants made their mark in 4-1 win vs. Peru</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
+          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0926/ss_20260926_205309109_36763731284/ss_20260926_205309109_36763731284.jpg</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
+          <t>https://www.espn.com/video/clip/_/id/50038230/usmnt-debutants-made-their-mark-4-1-win-vs-peru</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1009,27 +1009,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
+          <t>Pochettino shares 'regret' over Balogun controversy, impact on USMNT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
+          <t>USMNT coach Mauricio Pochettino said he regrets not being more involved in the process of appealing Folarin Balogun's suspension at this summer's World Cup, adding that the incident changed the energy around his squad.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721773_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
+          <t>https://www.espn.com/soccer/story/_/id/50028671/folarin-balogun-mauricio-pochettino-red-card-suspension-usa-world-cup</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1041,27 +1041,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
+          <t>Can Patrick Vieira rescue Senegal from their post-AFCON final hellscape?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
+          <t>Senegal, surely, must be asking what on earth they have done to receive the misfortune and wretched experiences they've endured since January, when they won, and then lost, the AFCON final.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0818/r1703391_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
+          <t>https://www.espn.com/espn/story/_/id/50025741/can-patrick-vieira-rescue-senegal-their-post-afcon-final-hellscape</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1073,27 +1073,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
+          <t>Premier League, LaLiga, Serie A, Bundesliga demand FIFA reform amid Gianni Infantino re-election bid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
+          <t>The top leagues in England, Italy, Germany and Spain have issued a joint-statement demanding governance reform at FIFA, amid Gianni Infantino's bid to be re-elected as president in 2027.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0925/r1721593_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
+          <t>https://www.espn.com/soccer/story/_/id/50025809/premier-league-bundesliga-la-liga-serie-gianni-infantino-fifa-reform-statement</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1105,27 +1105,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>Gianni Infantino says he is 'committed to doing what is right' for FIFA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guimaraes: World Cup penalty miss vs. Norway is a scar that still hurts</t>
+          <t>FIFA president Gianni Infantino says he has "never been more determined and committed" to doing "what is right for the game" after pledging to conduct an independent review of the organisation's governance.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0923/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts/dm_260923_Guimaraes_World_Cup_penalty_miss_vs_Norway_is_a_scar_that_still_hurts.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0808/r1699291_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50013350/world-cup-penalty-miss-vs-norway-scar-hurts</t>
+          <t>https://www.espn.com/soccer/story/_/id/50019011/gianni-infantino-says-committed-doing-right-fifa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1137,22 +1137,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA's Aleksander Ceferin: Trust still broken in football after FIFA, Gianni Infantino controversy</t>
+          <t>Gianni Infantino accused of 'woefully inadequate' co-operation with probe into Donald Trump links</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UEFA president Aleksander Ceferin has said trust in world football is still broken despite FIFA abandoning its controversial plan to sell a stake in its commercial rights to private investors.</t>
+          <t>FIFA president Gianni Infantino has been accused of a "woefully inadequate" level of co-operation over a probe by democratic members of the United States House Judiciary Committee into his relationship with Donald Trump.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://a.espncdn.com/photo/2026/0803/r1697001_1296x729_16-9.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0923/r1720984_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/50012609/trust-broken-football-fifa-gianni-infantino-uefa-aleksander-ceferin</t>
+          <t>https://www.espn.com/soccer/story/_/id/50015084/gianni-infantino-donald-trump-fifa-world-cup-uefa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1169,27 +1169,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>After Messi and Neymar, who will be next No. 10s for Brazil, Argentina?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gomez: Jonathan David and Julian Alvarez should play side-by-side</t>
+          <t>With Lionel Messi and Neymar set to leave the Argentina and Brazil teams, respectively, who will step up to wear two of South America's most historic shirts?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://espnmedia-cdn.akamaized.net/espn/media/common/2026/0922/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside/dm_260922_Gomez_Jonathan_David_and_Julian_Alvarez_should_play_sidebyside.jpg</t>
+          <t>https://a.espncdn.com/photo/2026/0922/r1720466_1296x729_16-9.jpg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.espn.com/video/clip/_/id/50004142/jonathan-david-julian-alvarez-play-side-side</t>
+          <t>https://www.espn.com/soccer/story/_/id/50006618/after-lionel-messi-neymar-brazil-argentinas-next-number-10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
